--- a/basedatos_partidas/salida/descompuestos/CT-05-04-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-04-040.xlsx
@@ -565,10 +565,10 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H11" t="n">
-        <v>10.62</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>6.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="H12" t="n">
-        <v>9.18</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="13">
@@ -617,10 +617,10 @@
         <v>1.08</v>
       </c>
       <c r="G13" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H13" t="n">
-        <v>4.54</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="14">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>44.99</v>
+        <v>43.81</v>
       </c>
     </row>
     <row r="22">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>53.9</v>
+        <v>52.72</v>
       </c>
       <c r="H33" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="34">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="5" t="n">
-        <v>54.44</v>
+        <v>53.25</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-05-04-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-04-040.xlsx
@@ -669,10 +669,10 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="16">
@@ -695,10 +695,10 @@
         <v>1.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H16" t="n">
-        <v>2.86</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="17">
@@ -721,10 +721,10 @@
         <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H17" t="n">
-        <v>2.79</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="18">
@@ -747,10 +747,10 @@
         <v>0.26</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.47</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="19">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>43.81</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="22">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>52.72</v>
+        <v>52.11</v>
       </c>
       <c r="H33" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="34">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="5" t="n">
-        <v>53.25</v>
+        <v>52.63</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-05-04-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-04-040.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 05 Estructuras</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Losas y entrepisos</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
